--- a/administrative_forms/005_project_plan_upload_form--administrative_forms.xlsx
+++ b/administrative_forms/005_project_plan_upload_form--administrative_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,20 +525,20 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Project Plan Upload</t>
+          <t>What is the project name?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Project Plan Details</t>
+          <t>Project description</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -571,20 +571,20 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>project_plan_upload_date</t>
+          <t>Project start date</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -594,20 +594,20 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Project Plan Upload</t>
+          <t>Project end date</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Project Plan Upload</t>
+          <t>Select project status</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,7 +630,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -640,20 +640,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Project Plan Upload</t>
+          <t>Choose relevant teams</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -663,13 +663,13 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Project Plan Upload</t>
+          <t>Upload project plan document</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Project Plan Upload</t>
+          <t>Project manager email</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -709,20 +709,20 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Project Plan Upload</t>
+          <t>Project budget</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Project Plan Upload</t>
+          <t>Additional notes</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,7 +745,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -755,20 +755,20 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Project Plan Upload</t>
+          <t>Expected completion date</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -778,82 +778,13 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Project Plan Upload</t>
+          <t>Select project type</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>project_plan_upload_form_page_13</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Project Plan Upload</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>project_plan_upload_form_page_14</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Project Plan Upload</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>project_plan_upload_form_page_15</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Project Plan Upload</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>yes</t>
         </is>
       </c>
     </row>
@@ -868,7 +799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -896,170 +827,187 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>project_plan_upload_form_page_6_choices</t>
+          <t>project_plan_upload_form_page_5_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>project_plan_upload_form_page_6_choices</t>
+          <t>project_plan_upload_form_page_5_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>project_plan_upload_form_page_6_choices</t>
+          <t>project_plan_upload_form_page_5_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>on-hold</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>On-hold</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>project_plan_upload_form_page_7_choices</t>
+          <t>project_plan_upload_form_page_5_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Canceled</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>project_plan_upload_form_page_7_choices</t>
+          <t>project_plan_upload_form_page_6_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>team_a</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Team A</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>project_plan_upload_form_page_7_choices</t>
+          <t>project_plan_upload_form_page_6_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>team_b</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Team B</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>project_plan_upload_form_page_7_choices</t>
+          <t>project_plan_upload_form_page_6_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option_4</t>
+          <t>team_c</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Option 4</t>
+          <t>Team C</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>project_plan_upload_form_page_15_choices</t>
+          <t>project_plan_upload_form_page_6_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>team_d</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Team D</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>project_plan_upload_form_page_15_choices</t>
+          <t>project_plan_upload_form_page_12_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>type_a</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Type A</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>project_plan_upload_form_page_15_choices</t>
+          <t>project_plan_upload_form_page_12_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>type_b</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Type B</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>project_plan_upload_form_page_12_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>type_c</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Type C</t>
         </is>
       </c>
     </row>
